--- a/0000_InglesConIA/verbos.xlsx
+++ b/0000_InglesConIA/verbos.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\0000_InglesConIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0C7E09-13B0-4463-8CF3-01C980F28FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2973832E-1B5E-432F-B6F8-B981EED7BD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_ToBe" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,29 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="206">
   <si>
     <t>I</t>
   </si>
   <si>
-    <t>he</t>
-  </si>
-  <si>
-    <t>she</t>
-  </si>
-  <si>
-    <t>it</t>
-  </si>
-  <si>
-    <t>we</t>
-  </si>
-  <si>
-    <t>they</t>
-  </si>
-  <si>
-    <t>you</t>
-  </si>
-  <si>
     <t>Pronombre</t>
   </si>
   <si>
@@ -216,12 +198,6 @@
     <t>NEGATIVA</t>
   </si>
   <si>
-    <t>PRESENTE SIMPLE</t>
-  </si>
-  <si>
-    <t>PRESENTE CONTINUO</t>
-  </si>
-  <si>
     <t>I am being</t>
   </si>
   <si>
@@ -369,9 +345,6 @@
     <t>they're not being</t>
   </si>
   <si>
-    <t>PRESENTE PERFECTO</t>
-  </si>
-  <si>
     <t>El Present Simple describe un estado, característica, identidad o ubicación actual</t>
   </si>
   <si>
@@ -523,6 +496,153 @@
   </si>
   <si>
     <t>nosotros hemos sido ? / nosotros hemos estado ?.</t>
+  </si>
+  <si>
+    <t>We</t>
+  </si>
+  <si>
+    <t>They</t>
+  </si>
+  <si>
+    <t>You</t>
+  </si>
+  <si>
+    <t>He</t>
+  </si>
+  <si>
+    <t>She</t>
+  </si>
+  <si>
+    <t>It</t>
+  </si>
+  <si>
+    <t>You were</t>
+  </si>
+  <si>
+    <t>We were</t>
+  </si>
+  <si>
+    <t>They were</t>
+  </si>
+  <si>
+    <t>I was</t>
+  </si>
+  <si>
+    <t>He was</t>
+  </si>
+  <si>
+    <t>She was</t>
+  </si>
+  <si>
+    <t>It was</t>
+  </si>
+  <si>
+    <t>yo era / yo estaba</t>
+  </si>
+  <si>
+    <t>el era / el estaba</t>
+  </si>
+  <si>
+    <t>tu eras / tu estabas</t>
+  </si>
+  <si>
+    <t>Ella era / Ella estaba</t>
+  </si>
+  <si>
+    <t>eso era / eso estaba</t>
+  </si>
+  <si>
+    <t>Nosotros eramos / nosotros estabamos</t>
+  </si>
+  <si>
+    <t>Ellos eran / ellos estaban</t>
+  </si>
+  <si>
+    <t>no tiene</t>
+  </si>
+  <si>
+    <t>were you ?</t>
+  </si>
+  <si>
+    <t>was He ?.</t>
+  </si>
+  <si>
+    <t>was She ?.</t>
+  </si>
+  <si>
+    <t>was it ?.</t>
+  </si>
+  <si>
+    <t>were We ?.</t>
+  </si>
+  <si>
+    <t>were They ?.</t>
+  </si>
+  <si>
+    <t>was I ?.</t>
+  </si>
+  <si>
+    <t>ella era / ella estaba</t>
+  </si>
+  <si>
+    <t>nosotros eramos / nosotros estabamos</t>
+  </si>
+  <si>
+    <t>ellos eran / ellos estaban</t>
+  </si>
+  <si>
+    <t>I was not</t>
+  </si>
+  <si>
+    <t>You were not</t>
+  </si>
+  <si>
+    <t>He was not</t>
+  </si>
+  <si>
+    <t>She was not</t>
+  </si>
+  <si>
+    <t>It was not</t>
+  </si>
+  <si>
+    <t>We were not</t>
+  </si>
+  <si>
+    <t>They were not</t>
+  </si>
+  <si>
+    <t>1 - PRESENTE SIMPLE</t>
+  </si>
+  <si>
+    <t>2 - PRESENTE CONTINUO</t>
+  </si>
+  <si>
+    <t>3 - PRESENTE PERFECTO</t>
+  </si>
+  <si>
+    <t>5 - PASADO</t>
+  </si>
+  <si>
+    <t>Yo no era / yo no estaba</t>
+  </si>
+  <si>
+    <t>Tu no eras / tu no estabas</t>
+  </si>
+  <si>
+    <t>El no era / El no estaba</t>
+  </si>
+  <si>
+    <t>Ella no era / Ella no estaba</t>
+  </si>
+  <si>
+    <t>Eso no era / Eso no estaba</t>
+  </si>
+  <si>
+    <t>Nosotros no eramos / nosotros no estabamos</t>
+  </si>
+  <si>
+    <t>Ellos no eran / Ellos no estaban</t>
   </si>
 </sst>
 </file>
@@ -598,11 +718,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -616,12 +739,13 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -902,48 +1026,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:K41"/>
+  <dimension ref="B2:K54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="62.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="66.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="48" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="65.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="70" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="50.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
+      <c r="B2" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -956,45 +1080,45 @@
       <c r="K4" s="8"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="G5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="J5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="K5" s="5"/>
+      <c r="B5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="G5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="J5" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K5" s="6"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
@@ -1002,263 +1126,263 @@
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="J7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="K7" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>6</v>
+        <v>159</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" t="s">
         <v>27</v>
       </c>
-      <c r="G8" t="s">
-        <v>33</v>
-      </c>
       <c r="H8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="K8" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
         <v>35</v>
       </c>
-      <c r="H9" t="s">
-        <v>41</v>
-      </c>
       <c r="J9" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="K9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>2</v>
+        <v>161</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" t="s">
         <v>36</v>
       </c>
-      <c r="H10" t="s">
-        <v>42</v>
-      </c>
       <c r="J10" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="K10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" t="s">
         <v>37</v>
       </c>
-      <c r="H11" t="s">
-        <v>43</v>
-      </c>
       <c r="J11" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K11" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>4</v>
+        <v>157</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" t="s">
         <v>38</v>
       </c>
-      <c r="H12" t="s">
-        <v>44</v>
-      </c>
       <c r="J12" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="K12" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>5</v>
+        <v>158</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" t="s">
         <v>39</v>
       </c>
-      <c r="H13" t="s">
-        <v>45</v>
-      </c>
       <c r="J13" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="K13" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
+      <c r="B16" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
+      <c r="B18" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="G19" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H19" s="4"/>
-      <c r="J19" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="K19" s="5"/>
+      <c r="B19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="G19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="J19" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K19" s="6"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
@@ -1266,210 +1390,210 @@
         <v>0</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E21" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G21" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="J21" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>6</v>
+        <v>159</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E22" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="J22" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="K22" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E23" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="G23" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="J23" t="s">
+        <v>94</v>
+      </c>
+      <c r="K23" t="s">
         <v>102</v>
-      </c>
-      <c r="K23" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>2</v>
+        <v>161</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E24" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G24" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="J24" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="C25" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E25" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="J25" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="K25" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>4</v>
+        <v>157</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D26" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E26" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G26" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H26" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="J26" t="s">
+        <v>96</v>
+      </c>
+      <c r="K26" t="s">
         <v>104</v>
-      </c>
-      <c r="K26" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>5</v>
+        <v>158</v>
       </c>
       <c r="C27" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D27" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E27" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="J27" t="s">
+        <v>97</v>
+      </c>
+      <c r="K27" t="s">
         <v>105</v>
       </c>
-      <c r="K27" t="s">
-        <v>113</v>
-      </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
+      <c r="B30" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-    </row>
-    <row r="32" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+    </row>
+    <row r="32" spans="2:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -1482,45 +1606,45 @@
       <c r="K32" s="2"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B33" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="G33" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H33" s="4"/>
-      <c r="J33" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="K33" s="5"/>
+      <c r="B33" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="G33" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H33" s="5"/>
+      <c r="J33" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K33" s="6"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
@@ -1528,185 +1652,458 @@
         <v>0</v>
       </c>
       <c r="C35" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D35" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="E35" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G35" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="H35" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="J35" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="K35" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>6</v>
+        <v>159</v>
       </c>
       <c r="C36" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D36" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E36" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="G36" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="H36" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="J36" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="K36" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D37" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E37" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="G37" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="H37" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="J37" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="K37" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>2</v>
+        <v>161</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D38" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E38" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="G38" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H38" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="J38" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="K38" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>3</v>
+        <v>162</v>
       </c>
       <c r="C39" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D39" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E39" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="G39" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="H39" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="J39" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="K39" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>4</v>
+        <v>157</v>
       </c>
       <c r="C40" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D40" t="s">
+        <v>117</v>
+      </c>
+      <c r="E40" t="s">
         <v>126</v>
       </c>
-      <c r="E40" t="s">
-        <v>135</v>
-      </c>
       <c r="G40" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="H40" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="J40" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="K40" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>5</v>
+        <v>158</v>
       </c>
       <c r="C41" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D41" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E41" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="G41" t="s">
+        <v>149</v>
+      </c>
+      <c r="H41" t="s">
+        <v>150</v>
+      </c>
+      <c r="J41" t="s">
+        <v>135</v>
+      </c>
+      <c r="K41" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B43" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+    </row>
+    <row r="45" spans="2:11" s="10" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B46" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="G46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H46" s="5"/>
+      <c r="J46" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K46" s="6"/>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" t="s">
+        <v>166</v>
+      </c>
+      <c r="D48" t="s">
+        <v>177</v>
+      </c>
+      <c r="E48" t="s">
+        <v>170</v>
+      </c>
+      <c r="G48" t="s">
+        <v>184</v>
+      </c>
+      <c r="H48" t="s">
+        <v>170</v>
+      </c>
+      <c r="J48" t="s">
+        <v>188</v>
+      </c>
+      <c r="K48" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>159</v>
+      </c>
+      <c r="C49" t="s">
+        <v>163</v>
+      </c>
+      <c r="D49" t="s">
+        <v>177</v>
+      </c>
+      <c r="E49" t="s">
+        <v>172</v>
+      </c>
+      <c r="G49" t="s">
+        <v>178</v>
+      </c>
+      <c r="H49" t="s">
+        <v>172</v>
+      </c>
+      <c r="J49" t="s">
+        <v>189</v>
+      </c>
+      <c r="K49" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>160</v>
+      </c>
+      <c r="C50" t="s">
+        <v>167</v>
+      </c>
+      <c r="D50" t="s">
+        <v>177</v>
+      </c>
+      <c r="E50" t="s">
+        <v>171</v>
+      </c>
+      <c r="G50" t="s">
+        <v>179</v>
+      </c>
+      <c r="H50" t="s">
+        <v>171</v>
+      </c>
+      <c r="J50" t="s">
+        <v>190</v>
+      </c>
+      <c r="K50" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>161</v>
+      </c>
+      <c r="C51" t="s">
+        <v>168</v>
+      </c>
+      <c r="D51" t="s">
+        <v>177</v>
+      </c>
+      <c r="E51" t="s">
+        <v>173</v>
+      </c>
+      <c r="G51" t="s">
+        <v>180</v>
+      </c>
+      <c r="H51" t="s">
+        <v>185</v>
+      </c>
+      <c r="J51" t="s">
+        <v>191</v>
+      </c>
+      <c r="K51" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>162</v>
+      </c>
+      <c r="C52" t="s">
+        <v>169</v>
+      </c>
+      <c r="D52" t="s">
+        <v>177</v>
+      </c>
+      <c r="E52" t="s">
+        <v>174</v>
+      </c>
+      <c r="G52" t="s">
+        <v>181</v>
+      </c>
+      <c r="H52" t="s">
+        <v>174</v>
+      </c>
+      <c r="J52" t="s">
+        <v>192</v>
+      </c>
+      <c r="K52" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>157</v>
+      </c>
+      <c r="C53" t="s">
+        <v>164</v>
+      </c>
+      <c r="D53" t="s">
+        <v>177</v>
+      </c>
+      <c r="E53" t="s">
+        <v>175</v>
+      </c>
+      <c r="G53" t="s">
+        <v>182</v>
+      </c>
+      <c r="H53" t="s">
+        <v>186</v>
+      </c>
+      <c r="J53" t="s">
+        <v>193</v>
+      </c>
+      <c r="K53" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
         <v>158</v>
       </c>
-      <c r="H41" t="s">
-        <v>159</v>
-      </c>
-      <c r="J41" t="s">
-        <v>144</v>
-      </c>
-      <c r="K41" t="s">
-        <v>151</v>
+      <c r="C54" t="s">
+        <v>165</v>
+      </c>
+      <c r="D54" t="s">
+        <v>177</v>
+      </c>
+      <c r="E54" t="s">
+        <v>176</v>
+      </c>
+      <c r="G54" t="s">
+        <v>183</v>
+      </c>
+      <c r="H54" t="s">
+        <v>187</v>
+      </c>
+      <c r="J54" t="s">
+        <v>194</v>
+      </c>
+      <c r="K54" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="18">
+    <mergeCell ref="B43:K44"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="B30:K31"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="J33:K33"/>
     <mergeCell ref="B18:K18"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="G5:H5"/>
@@ -1714,13 +2111,6 @@
     <mergeCell ref="B2:K3"/>
     <mergeCell ref="B16:K17"/>
     <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="B30:K31"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="J33:K33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/0000_InglesConIA/verbos.xlsx
+++ b/0000_InglesConIA/verbos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\0000_InglesConIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2973832E-1B5E-432F-B6F8-B981EED7BD3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB37E367-1C83-40BA-94EA-5A99E05E16D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_ToBe" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="207">
   <si>
     <t>I</t>
   </si>
@@ -643,6 +643,9 @@
   </si>
   <si>
     <t>Ellos no eran / Ellos no estaban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I </t>
   </si>
 </sst>
 </file>
@@ -718,14 +721,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -736,16 +739,12 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1026,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:K54"/>
+  <dimension ref="B2:K60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
@@ -1040,30 +1039,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
@@ -1304,44 +1303,44 @@
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
@@ -1568,30 +1567,30 @@
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
     </row>
     <row r="32" spans="2:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B32" s="2"/>
@@ -1830,42 +1829,42 @@
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-    </row>
-    <row r="45" spans="2:11" s="10" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="9"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+    </row>
+    <row r="45" spans="2:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="4" t="s">
@@ -2091,8 +2090,20 @@
         <v>205</v>
       </c>
     </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E60" t="s">
+        <v>206</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B18:K18"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="B2:K3"/>
+    <mergeCell ref="B16:K17"/>
+    <mergeCell ref="B4:K4"/>
     <mergeCell ref="B43:K44"/>
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="G46:H46"/>
@@ -2104,13 +2115,6 @@
     <mergeCell ref="B33:E33"/>
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="J33:K33"/>
-    <mergeCell ref="B18:K18"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="B2:K3"/>
-    <mergeCell ref="B16:K17"/>
-    <mergeCell ref="B4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/0000_InglesConIA/verbos.xlsx
+++ b/0000_InglesConIA/verbos.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00_ENGITHUB\Modulo02_JavaScript\0000_InglesConIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB37E367-1C83-40BA-94EA-5A99E05E16D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40DAC8D7-5F08-423D-AFD5-A793868BD8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_ToBe" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="298">
   <si>
     <t>I</t>
   </si>
@@ -645,7 +647,280 @@
     <t>Ellos no eran / Ellos no estaban</t>
   </si>
   <si>
-    <t xml:space="preserve">I </t>
+    <t>el ha sido / el ha estado</t>
+  </si>
+  <si>
+    <t>ella ha sido / ella ha estado</t>
+  </si>
+  <si>
+    <t>eso ha sido / eso ha estado</t>
+  </si>
+  <si>
+    <t>tu has sido / tu has estado</t>
+  </si>
+  <si>
+    <t>pronombre</t>
+  </si>
+  <si>
+    <t>traducción</t>
+  </si>
+  <si>
+    <t>afirmativa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">he has been </t>
+  </si>
+  <si>
+    <t xml:space="preserve">we have been </t>
+  </si>
+  <si>
+    <t>forma corta</t>
+  </si>
+  <si>
+    <t>have I been</t>
+  </si>
+  <si>
+    <t>have you been</t>
+  </si>
+  <si>
+    <t>has he been</t>
+  </si>
+  <si>
+    <t>has she been</t>
+  </si>
+  <si>
+    <t>has it been</t>
+  </si>
+  <si>
+    <t>have we been</t>
+  </si>
+  <si>
+    <t>have they been</t>
+  </si>
+  <si>
+    <t>he sido yo ?. / he estado yo ?.</t>
+  </si>
+  <si>
+    <t>has sido tu ?. / has estado tu ?.</t>
+  </si>
+  <si>
+    <t>ha sido el ?. / ha estado el ?.</t>
+  </si>
+  <si>
+    <t>ha sido ella ?. / ha estado ella ?.</t>
+  </si>
+  <si>
+    <t>ha sido eso ?. / ha estado eso ?.</t>
+  </si>
+  <si>
+    <t>hemos sido ?. / hemos estado ?.</t>
+  </si>
+  <si>
+    <t>han sido ellos ?. / han estado ellos ?.</t>
+  </si>
+  <si>
+    <t>Interrogativa</t>
+  </si>
+  <si>
+    <t>ellos no han sido / esos no han estado</t>
+  </si>
+  <si>
+    <t>negativa</t>
+  </si>
+  <si>
+    <t>yo estaba / yo era</t>
+  </si>
+  <si>
+    <t>you were</t>
+  </si>
+  <si>
+    <t>he was</t>
+  </si>
+  <si>
+    <t>she was</t>
+  </si>
+  <si>
+    <t>it was</t>
+  </si>
+  <si>
+    <t>we were</t>
+  </si>
+  <si>
+    <t>they were</t>
+  </si>
+  <si>
+    <t>was i ?.</t>
+  </si>
+  <si>
+    <t>were you ?.</t>
+  </si>
+  <si>
+    <t>was he ?</t>
+  </si>
+  <si>
+    <t>was she ?.</t>
+  </si>
+  <si>
+    <t>were we ?.</t>
+  </si>
+  <si>
+    <t>were they ?.</t>
+  </si>
+  <si>
+    <t>fui yo ?. Estuve yo ?.</t>
+  </si>
+  <si>
+    <t>fuiste tu ?. Estuviste tu ?.</t>
+  </si>
+  <si>
+    <t>fue el ?. Estuvo el ?.</t>
+  </si>
+  <si>
+    <t>fue ella ?. Estuvo ella ?.</t>
+  </si>
+  <si>
+    <t>fue eso ?. Estuvo eso ?.</t>
+  </si>
+  <si>
+    <t>fuimos nosotros ?. Estuvimos nosotros ?.</t>
+  </si>
+  <si>
+    <t>fueron ellos ?. Estuvieron ellos ?.</t>
+  </si>
+  <si>
+    <t>6 - FUTURO</t>
+  </si>
+  <si>
+    <t>it</t>
+  </si>
+  <si>
+    <t>will be</t>
+  </si>
+  <si>
+    <t>I'll be</t>
+  </si>
+  <si>
+    <t>you'll be</t>
+  </si>
+  <si>
+    <t>he'll be</t>
+  </si>
+  <si>
+    <t>she'll be</t>
+  </si>
+  <si>
+    <t>it'll be</t>
+  </si>
+  <si>
+    <t>We'll be</t>
+  </si>
+  <si>
+    <t>They'll be</t>
+  </si>
+  <si>
+    <t>yo seré / yo estaré</t>
+  </si>
+  <si>
+    <t>tu serás / tu estarás</t>
+  </si>
+  <si>
+    <t>el será / el estará</t>
+  </si>
+  <si>
+    <t>ella será / ella estará</t>
+  </si>
+  <si>
+    <t>eso será / eso estará</t>
+  </si>
+  <si>
+    <t>nosotros seremos / nosotros estaremos</t>
+  </si>
+  <si>
+    <t>ellos serán / ellos estarán</t>
+  </si>
+  <si>
+    <t>will i be ?</t>
+  </si>
+  <si>
+    <t>will you be ?.</t>
+  </si>
+  <si>
+    <t>will he be ?.</t>
+  </si>
+  <si>
+    <t>will she be ?.</t>
+  </si>
+  <si>
+    <t>will it be ?.</t>
+  </si>
+  <si>
+    <t>will we be ?</t>
+  </si>
+  <si>
+    <t>will they be ?.</t>
+  </si>
+  <si>
+    <t>seré yo ?. / estaré yo ?</t>
+  </si>
+  <si>
+    <t>serás tu ?. / estarás tu ?.</t>
+  </si>
+  <si>
+    <t>será el ?. / Estará el ?.</t>
+  </si>
+  <si>
+    <t>será ella ?. / Estará ella ?.</t>
+  </si>
+  <si>
+    <t>será eso ?. / estará eso ?.</t>
+  </si>
+  <si>
+    <t>serán ellos ?. / estarán ellos ?.</t>
+  </si>
+  <si>
+    <t>seremos nosotros ?. / estaremos nosotros ?.</t>
+  </si>
+  <si>
+    <t>I will not be</t>
+  </si>
+  <si>
+    <t>you will not be</t>
+  </si>
+  <si>
+    <t>he will not be</t>
+  </si>
+  <si>
+    <t>she wil not be</t>
+  </si>
+  <si>
+    <t>it will not be</t>
+  </si>
+  <si>
+    <t>we will not be</t>
+  </si>
+  <si>
+    <t>they will not be</t>
+  </si>
+  <si>
+    <t>yo no seré / yo no estaré</t>
+  </si>
+  <si>
+    <t>tu no serás / tu no estarás</t>
+  </si>
+  <si>
+    <t>el no será / el no estará</t>
+  </si>
+  <si>
+    <t>ella no será / ella no estará</t>
+  </si>
+  <si>
+    <t>eso no será / eso no estará</t>
+  </si>
+  <si>
+    <t>nosotros no seremos / nosotros no estaremos</t>
+  </si>
+  <si>
+    <t>ellos no serán / ellos no estarán</t>
   </si>
 </sst>
 </file>
@@ -721,12 +996,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -744,6 +1020,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1025,7 +1304,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:K60"/>
+  <dimension ref="B2:K68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
@@ -1039,60 +1318,60 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="G5" s="5" t="s">
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="G5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="J5" s="6" t="s">
+      <c r="H5" s="6"/>
+      <c r="J5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="K5" s="6"/>
+      <c r="K5" s="7"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
@@ -1303,60 +1582,60 @@
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="G19" s="5" t="s">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="G19" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H19" s="5"/>
-      <c r="J19" s="6" t="s">
+      <c r="H19" s="6"/>
+      <c r="J19" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="K19" s="6"/>
+      <c r="K19" s="7"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
@@ -1567,30 +1846,30 @@
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
     </row>
     <row r="32" spans="2:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B32" s="2"/>
@@ -1605,20 +1884,20 @@
       <c r="K32" s="2"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="G33" s="5" t="s">
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="G33" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H33" s="5"/>
-      <c r="J33" s="6" t="s">
+      <c r="H33" s="6"/>
+      <c r="J33" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="K33" s="6"/>
+      <c r="K33" s="7"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
@@ -1829,30 +2108,30 @@
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
     </row>
     <row r="45" spans="2:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="2"/>
@@ -1867,20 +2146,20 @@
       <c r="K45" s="2"/>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="G46" s="5" t="s">
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="G46" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H46" s="5"/>
-      <c r="J46" s="6" t="s">
+      <c r="H46" s="6"/>
+      <c r="J46" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="K46" s="6"/>
+      <c r="K46" s="7"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
@@ -2090,20 +2369,282 @@
         <v>205</v>
       </c>
     </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B57" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+    </row>
+    <row r="59" spans="2:11" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+    </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="E60" t="s">
-        <v>206</v>
+      <c r="B60" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="G60" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H60" s="6"/>
+      <c r="J60" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="K60" s="7"/>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B61" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" s="3"/>
+      <c r="G61" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>0</v>
+      </c>
+      <c r="C62" t="s">
+        <v>255</v>
+      </c>
+      <c r="D62" t="s">
+        <v>256</v>
+      </c>
+      <c r="E62" t="s">
+        <v>263</v>
+      </c>
+      <c r="G62" t="s">
+        <v>270</v>
+      </c>
+      <c r="H62" t="s">
+        <v>277</v>
+      </c>
+      <c r="J62" t="s">
+        <v>284</v>
+      </c>
+      <c r="K62" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>159</v>
+      </c>
+      <c r="C63" t="s">
+        <v>255</v>
+      </c>
+      <c r="D63" t="s">
+        <v>257</v>
+      </c>
+      <c r="E63" t="s">
+        <v>264</v>
+      </c>
+      <c r="G63" t="s">
+        <v>271</v>
+      </c>
+      <c r="H63" t="s">
+        <v>278</v>
+      </c>
+      <c r="J63" t="s">
+        <v>285</v>
+      </c>
+      <c r="K63" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>160</v>
+      </c>
+      <c r="C64" t="s">
+        <v>255</v>
+      </c>
+      <c r="D64" t="s">
+        <v>258</v>
+      </c>
+      <c r="E64" t="s">
+        <v>265</v>
+      </c>
+      <c r="G64" t="s">
+        <v>272</v>
+      </c>
+      <c r="H64" t="s">
+        <v>279</v>
+      </c>
+      <c r="J64" t="s">
+        <v>286</v>
+      </c>
+      <c r="K64" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>161</v>
+      </c>
+      <c r="C65" t="s">
+        <v>255</v>
+      </c>
+      <c r="D65" t="s">
+        <v>259</v>
+      </c>
+      <c r="E65" t="s">
+        <v>266</v>
+      </c>
+      <c r="G65" t="s">
+        <v>273</v>
+      </c>
+      <c r="H65" t="s">
+        <v>280</v>
+      </c>
+      <c r="J65" t="s">
+        <v>287</v>
+      </c>
+      <c r="K65" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>254</v>
+      </c>
+      <c r="C66" t="s">
+        <v>255</v>
+      </c>
+      <c r="D66" t="s">
+        <v>260</v>
+      </c>
+      <c r="E66" t="s">
+        <v>267</v>
+      </c>
+      <c r="G66" t="s">
+        <v>274</v>
+      </c>
+      <c r="H66" t="s">
+        <v>281</v>
+      </c>
+      <c r="J66" t="s">
+        <v>288</v>
+      </c>
+      <c r="K66" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>157</v>
+      </c>
+      <c r="C67" t="s">
+        <v>255</v>
+      </c>
+      <c r="D67" t="s">
+        <v>261</v>
+      </c>
+      <c r="E67" t="s">
+        <v>268</v>
+      </c>
+      <c r="G67" t="s">
+        <v>275</v>
+      </c>
+      <c r="H67" t="s">
+        <v>283</v>
+      </c>
+      <c r="J67" t="s">
+        <v>289</v>
+      </c>
+      <c r="K67" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>158</v>
+      </c>
+      <c r="C68" t="s">
+        <v>255</v>
+      </c>
+      <c r="D68" t="s">
+        <v>262</v>
+      </c>
+      <c r="E68" t="s">
+        <v>269</v>
+      </c>
+      <c r="G68" t="s">
+        <v>276</v>
+      </c>
+      <c r="H68" t="s">
+        <v>282</v>
+      </c>
+      <c r="J68" t="s">
+        <v>290</v>
+      </c>
+      <c r="K68" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B18:K18"/>
+  <mergeCells count="22">
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="B2:K3"/>
     <mergeCell ref="B16:K17"/>
     <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B57:K58"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="B18:K18"/>
     <mergeCell ref="B43:K44"/>
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="G46:H46"/>
@@ -2118,4 +2659,339 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B6FCCD4-E20F-495C-9766-C411F360CB75}">
+  <dimension ref="B2:J10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="48" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="F2" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="I2" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G3" t="s">
+        <v>211</v>
+      </c>
+      <c r="I3" t="s">
+        <v>210</v>
+      </c>
+      <c r="J3" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F4" t="s">
+        <v>216</v>
+      </c>
+      <c r="G4" t="s">
+        <v>223</v>
+      </c>
+      <c r="I4" t="s">
+        <v>129</v>
+      </c>
+      <c r="J4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" t="s">
+        <v>217</v>
+      </c>
+      <c r="G5" t="s">
+        <v>224</v>
+      </c>
+      <c r="I5" t="s">
+        <v>130</v>
+      </c>
+      <c r="J5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" t="s">
+        <v>206</v>
+      </c>
+      <c r="D6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" t="s">
+        <v>225</v>
+      </c>
+      <c r="I6" t="s">
+        <v>131</v>
+      </c>
+      <c r="J6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" t="s">
+        <v>207</v>
+      </c>
+      <c r="D7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F7" t="s">
+        <v>219</v>
+      </c>
+      <c r="G7" t="s">
+        <v>226</v>
+      </c>
+      <c r="I7" t="s">
+        <v>132</v>
+      </c>
+      <c r="J7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F8" t="s">
+        <v>220</v>
+      </c>
+      <c r="G8" t="s">
+        <v>227</v>
+      </c>
+      <c r="I8" t="s">
+        <v>133</v>
+      </c>
+      <c r="J8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9" t="s">
+        <v>221</v>
+      </c>
+      <c r="G9" t="s">
+        <v>228</v>
+      </c>
+      <c r="I9" t="s">
+        <v>134</v>
+      </c>
+      <c r="J9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F10" t="s">
+        <v>222</v>
+      </c>
+      <c r="G10" t="s">
+        <v>229</v>
+      </c>
+      <c r="I10" t="s">
+        <v>135</v>
+      </c>
+      <c r="J10" t="s">
+        <v>231</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="I2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{840FF2AC-8B1F-42F6-AAC5-E0CB576488B0}">
+  <dimension ref="B3:F9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" t="s">
+        <v>171</v>
+      </c>
+      <c r="E5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E6" t="s">
+        <v>243</v>
+      </c>
+      <c r="F6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>237</v>
+      </c>
+      <c r="C7" t="s">
+        <v>174</v>
+      </c>
+      <c r="E7" t="s">
+        <v>181</v>
+      </c>
+      <c r="F7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F8" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C9" t="s">
+        <v>187</v>
+      </c>
+      <c r="E9" t="s">
+        <v>245</v>
+      </c>
+      <c r="F9" t="s">
+        <v>252</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>